--- a/artfynd/A 36104-2021 artfynd.xlsx
+++ b/artfynd/A 36104-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36104-2021 artfynd.xlsx
+++ b/artfynd/A 36104-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>19799562</v>
+        <v>19817056</v>
       </c>
       <c r="B2" t="n">
-        <v>56811</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102999</v>
+        <v>100011</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Aquila chrysaetos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608721.7252066964</v>
+        <v>608722</v>
       </c>
       <c r="R2" t="n">
-        <v>7280279.787367813</v>
+        <v>7280280</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
@@ -755,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,16 +789,11 @@
         <v>19801424</v>
       </c>
       <c r="B3" t="n">
-        <v>55607</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -841,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608721.7252066964</v>
+        <v>608722</v>
       </c>
       <c r="R3" t="n">
-        <v>7280279.787367813</v>
+        <v>7280280</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
@@ -913,15 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>19817056</v>
+        <v>47492684</v>
       </c>
       <c r="B4" t="n">
-        <v>56277</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,16 +913,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100011</v>
+        <v>102621</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsörn</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aquila chrysaetos</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -951,16 +935,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Akerträskberget, Örnäsudden, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608721.7252066964</v>
+        <v>608722</v>
       </c>
       <c r="R4" t="n">
-        <v>7280279.787367813</v>
+        <v>7280280</v>
       </c>
       <c r="S4" t="n">
         <v>2</v>
@@ -987,22 +976,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2004-06-06</t>
+          <t>2013-11-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2004-06-06</t>
+          <t>2013-11-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>i trädtopp vid Akersträskvgn</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,22 +1016,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström</t>
+          <t>Via Bernt-Erik Nordenström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>19801423</v>
+        <v>19799890</v>
       </c>
       <c r="B5" t="n">
-        <v>56886</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,16 +1034,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102995</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,14 +1051,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1078,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>608721.7252066964</v>
+        <v>608722</v>
       </c>
       <c r="R5" t="n">
-        <v>7280279.787367813</v>
+        <v>7280280</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1113,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,37 +1135,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>46270866</v>
+        <v>19801423</v>
       </c>
       <c r="B6" t="n">
-        <v>56806</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>102995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1199,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>608721.7252066964</v>
+        <v>608722</v>
       </c>
       <c r="R6" t="n">
-        <v>7280279.787367813</v>
+        <v>7280280</v>
       </c>
       <c r="S6" t="n">
         <v>2</v>
@@ -1229,22 +1209,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-06-15</t>
+          <t>2004-06-06</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-06-15</t>
+          <t>2004-06-06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1271,15 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>47447625</v>
+        <v>19799562</v>
       </c>
       <c r="B7" t="n">
-        <v>56542</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,31 +1262,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103022</v>
+        <v>102999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappmes</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile cinctus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1320,10 +1291,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>608721.7252066964</v>
+        <v>608722</v>
       </c>
       <c r="R7" t="n">
-        <v>7280279.787367813</v>
+        <v>7280280</v>
       </c>
       <c r="S7" t="n">
         <v>2</v>
@@ -1350,27 +1321,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2013-10-06</t>
+          <t>2004-06-06</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2013-10-06</t>
+          <t>2004-06-06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Daniel Häggström</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,10 +1356,363 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
+          <t>Bernt-Erik Nordenström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>46270866</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58388</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Akerträskberget, Örnäsudden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>608722</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7280280</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2013-06-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2013-06-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bernt-Erik Nordenström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bernt-Erik Nordenström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>19801425</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Akerträskberget, Örnäsudden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>608722</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7280280</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2004-06-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2004-06-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bernt-Erik Nordenström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bernt-Erik Nordenström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>47447625</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58116</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103022</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lappmes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile cinctus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Boddaert, 1783)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Akerträskberget, Örnäsudden, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>608722</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7280280</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2013-10-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2013-10-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Daniel Häggström</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bernt-Erik Nordenström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
           <t>Via Bernt-Erik Nordenström</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
